--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33395F0E-3065-9D4E-A400-01EE46D205BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D81281-49DB-1049-ABDF-7FF1FFD8005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="19200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -172,13 +172,13 @@
     <t>12/12/25 – 20/04/24</t>
   </si>
   <si>
-    <t>RoomBooking</t>
-  </si>
-  <si>
-    <t>23/02/2026 – 17/03/26</t>
-  </si>
-  <si>
     <t>N° candidat : 2543689137</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>21/10/2025 – 17/03/26</t>
   </si>
 </sst>
 </file>
@@ -636,6 +636,30 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,30 +668,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -948,56 +948,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1009,22 +1009,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1047,8 +1047,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
@@ -1069,16 +1069,16 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
@@ -1181,16 +1181,16 @@
       <c r="H18" s="14"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
@@ -1283,16 +1283,16 @@
       <c r="H26" s="14"/>
     </row>
     <row r="27" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
@@ -1410,20 +1410,20 @@
     </row>
     <row r="33" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>20</v>
-      </c>
+      <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="H33" s="21" t="s">
         <v>20</v>
       </c>
@@ -1431,12 +1431,12 @@
     <row r="34" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="15"/>
       <c r="B34" s="16"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="34"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="25"/>
     </row>
     <row r="35" spans="1:8" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A35" s="17"/>
@@ -1496,6 +1496,11 @@
     <row r="81" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A4:E4"/>
@@ -1503,11 +1508,6 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D81281-49DB-1049-ABDF-7FF1FFD8005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90BFD585-F1D0-0247-84FA-199E46437B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2560" yWindow="600" windowWidth="30720" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -642,6 +642,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -659,15 +668,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -948,56 +948,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1009,22 +1009,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="33" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1047,8 +1047,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
@@ -1069,16 +1069,16 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
@@ -1181,16 +1181,16 @@
       <c r="H18" s="14"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
@@ -1283,16 +1283,16 @@
       <c r="H26" s="14"/>
     </row>
     <row r="27" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
@@ -1351,9 +1351,7 @@
       <c r="D30" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>20</v>
-      </c>
+      <c r="E30" s="12"/>
       <c r="F30" s="12" t="s">
         <v>20</v>
       </c>
@@ -1496,11 +1494,6 @@
     <row r="81" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A4:E4"/>
@@ -1508,6 +1501,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90BFD585-F1D0-0247-84FA-199E46437B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47F02986-F4E6-2749-A270-42C72CC460F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2560" yWindow="600" windowWidth="30720" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="19200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,12 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -179,6 +176,15 @@
   </si>
   <si>
     <t>21/10/2025 – 17/03/26</t>
+  </si>
+  <si>
+    <t>PluvitechTools</t>
+  </si>
+  <si>
+    <t>12/01/2026 –  26/02/2026</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
   </si>
 </sst>
 </file>
@@ -504,58 +510,56 @@
       <left style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
       <right style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
       <top style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
       <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
@@ -565,7 +569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -609,11 +613,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -636,11 +637,26 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -651,23 +667,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -937,7 +947,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="70.5" style="1" customWidth="1"/>
@@ -948,217 +958,309 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="A3" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="A4" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+    </row>
+    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="B6" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="31" t="s">
+      <c r="B12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-    </row>
-    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-    </row>
-    <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="21"/>
-    </row>
-    <row r="11" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="21"/>
-    </row>
-    <row r="12" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14"/>
+      <c r="B13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+      <c r="A14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="20" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="15" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
+      <c r="A15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
@@ -1170,282 +1272,83 @@
       <c r="G17" s="13"/>
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A19" s="29" t="s">
+    <row r="18" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+      <c r="A18" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
+    </row>
+    <row r="19" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-    </row>
-    <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="14"/>
-    </row>
-    <row r="22" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="14"/>
-    </row>
-    <row r="23" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="14"/>
-    </row>
-    <row r="25" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="14"/>
-    </row>
-    <row r="26" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="14"/>
-    </row>
-    <row r="27" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A27" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-    </row>
-    <row r="28" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="23" t="s">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
+    </row>
+    <row r="21" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="15"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" spans="1:8" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A35" s="17"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-    </row>
+      <c r="B21" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:8" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" spans="1:8" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A34" s="16"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+    </row>
+    <row r="35" spans="1:8" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="36" spans="1:8" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="37" spans="1:8" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="38" spans="1:8" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
@@ -1491,21 +1394,20 @@
     <row r="78" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="79" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="80" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="81" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47F02986-F4E6-2749-A270-42C72CC460F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E252EB-5A15-E347-A613-2C9EAF11557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="19200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>MisterPizzaPlugin</t>
+  </si>
+  <si>
+    <t>09/09/2023 –  09/09/2024</t>
   </si>
 </sst>
 </file>
@@ -569,7 +575,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -643,6 +649,27 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -658,25 +685,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -958,56 +967,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1019,22 +1028,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1057,8 +1066,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="27"/>
-      <c r="B7" s="28"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
@@ -1079,16 +1088,16 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
@@ -1187,7 +1196,9 @@
       <c r="D13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="12"/>
+      <c r="E13" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="F13" s="12" t="s">
         <v>19</v>
       </c>
@@ -1253,7 +1264,9 @@
         <v>19</v>
       </c>
       <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="E16" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
         <v>19</v>
@@ -1273,44 +1286,54 @@
       <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14"/>
+      <c r="A19" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="31"/>
     </row>
     <row r="21" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="25" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="23" t="s">
@@ -1396,11 +1419,6 @@
     <row r="80" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A4:E4"/>
@@ -1408,6 +1426,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E252EB-5A15-E347-A613-2C9EAF11557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4185A7-113C-0449-BA56-142041AEA467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>09/09/2023 –  09/09/2024</t>
+  </si>
+  <si>
+    <t>∑</t>
   </si>
 </sst>
 </file>
@@ -652,6 +655,33 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -660,33 +690,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -967,56 +970,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="26"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1028,22 +1031,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="33" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1066,8 +1069,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="34"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
@@ -1088,16 +1091,16 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
@@ -1286,22 +1289,22 @@
       <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="31"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -1318,16 +1321,16 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="31"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
@@ -1351,7 +1354,11 @@
     </row>
     <row r="22" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="23" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H24" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="25" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="26" spans="1:8" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="27" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1419,6 +1426,11 @@
     <row r="80" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A4:E4"/>
@@ -1426,16 +1438,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="50" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4185A7-113C-0449-BA56-142041AEA467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1935D3EB-9869-4A44-85C3-93C9538E06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -121,9 +121,6 @@
     <t>NOM et prénom : Lyulchak Denys</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : https://plumcreativ.github.io/Denys_Portfolio/</t>
-  </si>
-  <si>
     <t>MediaSchool</t>
   </si>
   <si>
@@ -193,7 +190,7 @@
     <t>09/09/2023 –  09/09/2024</t>
   </si>
   <si>
-    <t>∑</t>
+    <t>Adresse URL du portfolio :  https://plumcreativ.github.io/Denys_Portfolio/</t>
   </si>
 </sst>
 </file>
@@ -203,7 +200,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* \-??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -285,6 +282,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -574,11 +585,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -658,6 +670,15 @@
     <xf numFmtId="16" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -670,9 +691,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -682,18 +700,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -970,56 +987,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="35"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1027,26 +1044,27 @@
         <v>3</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-    </row>
-    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="M5" s="38"/>
+    </row>
+    <row r="6" spans="1:13" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="35" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1069,8 +1087,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="9" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
@@ -1091,23 +1109,23 @@
       </c>
     </row>
     <row r="8" spans="1:13" s="9" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>19</v>
@@ -1124,10 +1142,10 @@
     </row>
     <row r="10" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>19</v>
@@ -1144,10 +1162,10 @@
     </row>
     <row r="11" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>19</v>
@@ -1168,10 +1186,10 @@
     </row>
     <row r="12" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>19</v>
@@ -1188,10 +1206,10 @@
     </row>
     <row r="13" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>19</v>
@@ -1214,10 +1232,10 @@
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>19</v>
@@ -1234,10 +1252,10 @@
     </row>
     <row r="15" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>19</v>
@@ -1258,10 +1276,10 @@
     </row>
     <row r="16" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>42</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>19</v>
@@ -1289,23 +1307,23 @@
       <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.15">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>46</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>47</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>19</v>
@@ -1321,23 +1339,23 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="32"/>
     </row>
     <row r="21" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>44</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>19</v>
@@ -1354,11 +1372,7 @@
     </row>
     <row r="22" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="23" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H24" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
+    <row r="24" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="25" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="26" spans="1:8" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
     <row r="27" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1426,11 +1440,6 @@
     <row r="80" customFormat="1" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A4:E4"/>
@@ -1438,11 +1447,19 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="8" scale="50" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink ref="A5:H5" r:id="rId1" display="Adresse URL du portfolio :  https://plumcreativ.github.io/Denys_Portfolio/" xr:uid="{088F42D3-0662-3B44-9B41-1D008E8085FE}"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="65" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
+++ b/src/BTS SIO - Tableau de synthèse - Epreuve E4 - BTS SIO 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin-27904/Documents/Protfolio/Denys_Portfolio/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1935D3EB-9869-4A44-85C3-93C9538E06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A493C426-E6DB-B547-88FD-C08543C9F9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="17340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="48">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -121,9 +121,6 @@
     <t>NOM et prénom : Lyulchak Denys</t>
   </si>
   <si>
-    <t>MediaSchool</t>
-  </si>
-  <si>
     <t xml:space="preserve">03/10/2025 – 07/11/2025  </t>
   </si>
   <si>
@@ -157,15 +154,9 @@
     <t>10/02/23 – 20/03/23</t>
   </si>
   <si>
-    <t>10/10/24 – 02/11/24</t>
-  </si>
-  <si>
     <t>CryptoVault</t>
   </si>
   <si>
-    <t>12/12/25 – 20/04/24</t>
-  </si>
-  <si>
     <t>N° candidat : 2543689137</t>
   </si>
   <si>
@@ -178,9 +169,6 @@
     <t>PluvitechTools</t>
   </si>
   <si>
-    <t>12/01/2026 –  26/02/2026</t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
@@ -191,6 +179,18 @@
   </si>
   <si>
     <t>Adresse URL du portfolio :  https://plumcreativ.github.io/Denys_Portfolio/</t>
+  </si>
+  <si>
+    <t>12/12/25 – 20/03/25</t>
+  </si>
+  <si>
+    <t>12/01/2026 –  21/02/2026</t>
+  </si>
+  <si>
+    <t>10/04/23 – 02/05/23</t>
+  </si>
+  <si>
+    <t>MediaStock</t>
   </si>
 </sst>
 </file>
@@ -996,7 +996,7 @@
       <c r="E1" s="27"/>
       <c r="F1" s="27"/>
       <c r="G1" s="27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H1" s="27"/>
     </row>
@@ -1021,7 +1021,7 @@
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
       <c r="F3" s="29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
@@ -1044,12 +1044,12 @@
         <v>3</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="9" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>32</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>19</v>
@@ -1135,17 +1135,15 @@
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>19</v>
@@ -1155,17 +1153,15 @@
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>19</v>
@@ -1177,19 +1173,17 @@
       <c r="F11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>19</v>
@@ -1206,10 +1200,10 @@
     </row>
     <row r="13" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>19</v>
@@ -1232,10 +1226,10 @@
     </row>
     <row r="14" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>19</v>
@@ -1252,10 +1246,10 @@
     </row>
     <row r="15" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>19</v>
@@ -1276,10 +1270,10 @@
     </row>
     <row r="16" spans="1:13" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>19</v>
@@ -1320,10 +1314,10 @@
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>19</v>
@@ -1352,10 +1346,10 @@
     </row>
     <row r="21" spans="1:8" s="9" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>19</v>
